--- a/Nubank_Case_Performer/Data/Temp/Relatorio_Vendas_NJ TOLENTINO.xlsx
+++ b/Nubank_Case_Performer/Data/Temp/Relatorio_Vendas_NJ TOLENTINO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\Documents\UiPath\Nubank_Case_Performer\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CEB8C7-4707-44C3-BCD4-53F18EB8DE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E1532-7657-4712-B8B6-7AC559383E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2505" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{ID_VENDOR}" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
     <t>IT145632</t>
   </si>
   <si>
-    <t>29/04/2026</t>
+    <t>05/05/2026</t>
   </si>
   <si>
     <t>NJ TOLENTINO</t>
@@ -116,7 +116,7 @@
     <t>867556 / Beverages and Catering</t>
   </si>
   <si>
-    <t>Please, GENERATE INVOICES by 04/05/2026</t>
+    <t>Please, GENERATE INVOICES by 10/05/2026</t>
   </si>
 </sst>
 </file>
@@ -1452,14 +1452,14 @@
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="45">
-        <v>149467.75</v>
+        <v>147739.97</v>
       </c>
       <c r="E18" s="46">
         <v>8</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="45">
-        <v>1195742.03</v>
+        <v>1181919.73</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="1"/>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="C19" s="44"/>
       <c r="D19" s="47">
-        <v>12277.33</v>
+        <v>12052.06</v>
       </c>
       <c r="E19" s="46">
         <v>8</v>
       </c>
       <c r="F19" s="44"/>
       <c r="G19" s="45">
-        <v>98218.66</v>
+        <v>96416.5</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="1"/>
@@ -1524,14 +1524,14 @@
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="47">
-        <v>1668824.22</v>
+        <v>1638203.78</v>
       </c>
       <c r="E20" s="46">
         <v>1</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="45">
-        <v>1668824.22</v>
+        <v>1638203.78</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="1"/>
@@ -1560,14 +1560,14 @@
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="47">
-        <v>45333.31</v>
+        <v>44809.27</v>
       </c>
       <c r="E21" s="46">
         <v>10</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="45">
-        <v>453333.08</v>
+        <v>448092.73</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="1"/>
@@ -1770,7 +1770,7 @@
       <c r="F27" s="56"/>
       <c r="G27" s="57">
         <f>SUM(G18:G25)</f>
-        <v>3416117.99</v>
+        <v>3364632.7399999998</v>
       </c>
       <c r="H27" s="20"/>
       <c r="I27" s="1"/>
@@ -1796,7 +1796,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="58">
         <f>G31</f>
-        <v>3228231.4995000004</v>
+        <v>3179577.9434999996</v>
       </c>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F28" s="56"/>
       <c r="G28" s="57">
-        <v>341611.8</v>
+        <v>336463.27</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="1"/>
@@ -1870,7 +1870,7 @@
       <c r="F30" s="56"/>
       <c r="G30" s="57">
         <f>(G27-G28)*G29</f>
-        <v>153725.30950000003</v>
+        <v>151408.47349999999</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="1"/>
@@ -1903,7 +1903,7 @@
       <c r="F31" s="56"/>
       <c r="G31" s="57">
         <f>G27-G28+G30</f>
-        <v>3228231.4995000004</v>
+        <v>3179577.9434999996</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="1"/>

--- a/Nubank_Case_Performer/Data/Temp/Relatorio_Vendas_NJ TOLENTINO.xlsx
+++ b/Nubank_Case_Performer/Data/Temp/Relatorio_Vendas_NJ TOLENTINO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\Documents\UiPath\Nubank_Case_Performer\Data\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\Documents\StevanBOT_Git\Nubank_Case_Performer\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E1532-7657-4712-B8B6-7AC559383E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8A8864-63EA-404A-B7A8-6CEC3D59AAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{ID_VENDOR}" sheetId="1" r:id="rId1"/>
@@ -1452,14 +1452,14 @@
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="45">
-        <v>147739.97</v>
+        <v>147229.29999999999</v>
       </c>
       <c r="E18" s="46">
         <v>8</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="45">
-        <v>1181919.73</v>
+        <v>1177834.3700000001</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="1"/>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="C19" s="44"/>
       <c r="D19" s="47">
-        <v>12052.06</v>
+        <v>12059.79</v>
       </c>
       <c r="E19" s="46">
         <v>8</v>
       </c>
       <c r="F19" s="44"/>
       <c r="G19" s="45">
-        <v>96416.5</v>
+        <v>96478.36</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="1"/>
@@ -1524,14 +1524,14 @@
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="47">
-        <v>1638203.78</v>
+        <v>1639254.84</v>
       </c>
       <c r="E20" s="46">
         <v>1</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="45">
-        <v>1638203.78</v>
+        <v>1639254.84</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="1"/>
@@ -1560,14 +1560,14 @@
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="47">
-        <v>44809.27</v>
+        <v>44654.39</v>
       </c>
       <c r="E21" s="46">
         <v>10</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="45">
-        <v>448092.73</v>
+        <v>446543.88</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="1"/>
@@ -1770,7 +1770,7 @@
       <c r="F27" s="56"/>
       <c r="G27" s="57">
         <f>SUM(G18:G25)</f>
-        <v>3364632.7399999998</v>
+        <v>3360111.45</v>
       </c>
       <c r="H27" s="20"/>
       <c r="I27" s="1"/>
@@ -1796,7 +1796,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="58">
         <f>G31</f>
-        <v>3179577.9434999996</v>
+        <v>3175305.3255000003</v>
       </c>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F28" s="56"/>
       <c r="G28" s="57">
-        <v>336463.27</v>
+        <v>336011.14</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="1"/>
@@ -1870,7 +1870,7 @@
       <c r="F30" s="56"/>
       <c r="G30" s="57">
         <f>(G27-G28)*G29</f>
-        <v>151408.47349999999</v>
+        <v>151205.01550000001</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="1"/>
@@ -1903,7 +1903,7 @@
       <c r="F31" s="56"/>
       <c r="G31" s="57">
         <f>G27-G28+G30</f>
-        <v>3179577.9434999996</v>
+        <v>3175305.3255000003</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="1"/>
